--- a/3-语料与资格索引（数据表）.xlsx
+++ b/3-语料与资格索引（数据表）.xlsx
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -76,6 +76,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5400,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W236"/>
+  <dimension ref="A1:X236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5426,6 +5429,7 @@
     <col width="8" customWidth="1" min="21" max="21"/>
     <col width="46" customWidth="1" min="22" max="22"/>
     <col width="45" customWidth="1" min="23" max="23"/>
+    <col width="76" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5445,7 +5449,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>说明：含效应量标识、研究序号、结局变量与时点、资格类别、任务差异类型、迁移距离、证据档位、缺口代码、闸门、集合归属、效应量与方差、题录与全文相对路径。</t>
+          <t>说明：含效应量标识、研究序号、结局变量与时点、资格类别、任务差异类型、迁移距离、证据档位、缺口代码、闸门、集合归属、效应量与方差、题录与全文相对路径及正文分析处理。</t>
         </is>
       </c>
     </row>
@@ -5565,6 +5569,11 @@
           <t>TXT相对文件</t>
         </is>
       </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>正文分析处理</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -5682,6 +5691,7 @@
           <t>纳入研究全文/文本/02_Tang_2026.txt</t>
         </is>
       </c>
+      <c r="X6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5799,6 +5809,7 @@
           <t>纳入研究全文/文本/03_Guo_2026.txt</t>
         </is>
       </c>
+      <c r="X7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -5916,6 +5927,7 @@
           <t>纳入研究全文/文本/03_Guo_2026.txt</t>
         </is>
       </c>
+      <c r="X8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -6033,6 +6045,7 @@
           <t>纳入研究全文/文本/03_Guo_2026.txt</t>
         </is>
       </c>
+      <c r="X9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -6150,6 +6163,7 @@
           <t>纳入研究全文/文本/03_Guo_2026.txt</t>
         </is>
       </c>
+      <c r="X10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -6267,6 +6281,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6384,6 +6399,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6501,6 +6517,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -6618,6 +6635,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -6735,6 +6753,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -6852,6 +6871,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -6969,6 +6989,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -7086,6 +7107,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -7203,6 +7225,7 @@
           <t>纳入研究全文/文本/04_Wang_2026.txt</t>
         </is>
       </c>
+      <c r="X19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7320,6 +7343,7 @@
           <t>纳入研究全文/文本/08_Chen_2026.txt</t>
         </is>
       </c>
+      <c r="X20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -7437,6 +7461,7 @@
           <t>纳入研究全文/文本/11_Xiao_2026.txt</t>
         </is>
       </c>
+      <c r="X21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -7554,6 +7579,7 @@
           <t>纳入研究全文/文本/14_Omeh_2025.txt</t>
         </is>
       </c>
+      <c r="X22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -7671,6 +7697,7 @@
           <t>纳入研究全文/文本/14_Omeh_2025.txt</t>
         </is>
       </c>
+      <c r="X23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -7788,6 +7815,7 @@
           <t>纳入研究全文/文本/15_Yang_2025.txt</t>
         </is>
       </c>
+      <c r="X24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -7905,6 +7933,7 @@
           <t>纳入研究全文/文本/15_Yang_2025.txt</t>
         </is>
       </c>
+      <c r="X25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -8022,6 +8051,7 @@
           <t>纳入研究全文/文本/15_Yang_2025.txt</t>
         </is>
       </c>
+      <c r="X26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -8139,6 +8169,7 @@
           <t>纳入研究全文/文本/18_Zhao_2025.txt</t>
         </is>
       </c>
+      <c r="X27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -8256,6 +8287,7 @@
           <t>纳入研究全文/文本/18_Zhao_2025.txt</t>
         </is>
       </c>
+      <c r="X28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -8373,6 +8405,7 @@
           <t>纳入研究全文/文本/19_Huang_2025.txt</t>
         </is>
       </c>
+      <c r="X29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -8490,6 +8523,7 @@
           <t>纳入研究全文/文本/19_Huang_2025.txt</t>
         </is>
       </c>
+      <c r="X30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -8607,6 +8641,7 @@
           <t>纳入研究全文/文本/19_Huang_2025.txt</t>
         </is>
       </c>
+      <c r="X31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -8724,6 +8759,7 @@
           <t>纳入研究全文/文本/19_Huang_2025.txt</t>
         </is>
       </c>
+      <c r="X32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -8841,6 +8877,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -8958,6 +8995,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -9075,6 +9113,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -9192,6 +9231,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -9309,6 +9349,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -9426,6 +9467,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -9543,6 +9585,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -9660,6 +9703,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -9777,6 +9821,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -9894,6 +9939,7 @@
           <t>纳入研究全文/文本/21_Wu_2025.txt</t>
         </is>
       </c>
+      <c r="X42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -10011,6 +10057,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -10128,6 +10175,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -10245,6 +10293,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -10362,6 +10411,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -10479,6 +10529,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -10596,6 +10647,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -10713,6 +10765,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -10830,6 +10883,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -10947,6 +11001,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -11064,6 +11119,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -11181,6 +11237,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -11298,6 +11355,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -11415,6 +11473,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -11532,6 +11591,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -11649,6 +11709,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -11766,6 +11827,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -11883,6 +11945,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -12000,6 +12063,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -12117,6 +12181,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -12234,6 +12299,7 @@
           <t>纳入研究全文/文本/24_Gong_2025.txt</t>
         </is>
       </c>
+      <c r="X62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -12351,6 +12417,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -12468,6 +12535,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -12585,6 +12653,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -12702,6 +12771,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -12819,6 +12889,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -12936,6 +13007,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -13053,6 +13125,7 @@
           <t>纳入研究全文/文本/25_林裕如_2025.txt</t>
         </is>
       </c>
+      <c r="X69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -13170,6 +13243,7 @@
           <t>纳入研究全文/文本/26_冯友梅_2025.txt</t>
         </is>
       </c>
+      <c r="X70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -13287,6 +13361,7 @@
           <t>纳入研究全文/文本/26_冯友梅_2025.txt</t>
         </is>
       </c>
+      <c r="X71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -13404,6 +13479,7 @@
           <t>纳入研究全文/文本/26_冯友梅_2025.txt</t>
         </is>
       </c>
+      <c r="X72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -13521,6 +13597,7 @@
           <t>纳入研究全文/文本/26_冯友梅_2025.txt</t>
         </is>
       </c>
+      <c r="X73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -13638,6 +13715,7 @@
           <t>纳入研究全文/文本/35_王悦_2024.txt</t>
         </is>
       </c>
+      <c r="X74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -13755,6 +13833,7 @@
           <t>纳入研究全文/文本/35_王悦_2024.txt</t>
         </is>
       </c>
+      <c r="X75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -13872,6 +13951,7 @@
           <t>纳入研究全文/文本/35_王悦_2024.txt</t>
         </is>
       </c>
+      <c r="X76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -13989,6 +14069,7 @@
           <t>纳入研究全文/文本/35_王悦_2024.txt</t>
         </is>
       </c>
+      <c r="X77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -14106,6 +14187,7 @@
           <t>纳入研究全文/文本/36_Yadav_2023.txt</t>
         </is>
       </c>
+      <c r="X78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -14223,6 +14305,7 @@
           <t>纳入研究全文/文本/36_Yadav_2023.txt</t>
         </is>
       </c>
+      <c r="X79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -14340,6 +14423,7 @@
           <t>纳入研究全文/文本/36_Yadav_2023.txt</t>
         </is>
       </c>
+      <c r="X80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -14457,6 +14541,7 @@
           <t>纳入研究全文/文本/36_Yadav_2023.txt</t>
         </is>
       </c>
+      <c r="X81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -14574,6 +14659,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -14691,6 +14777,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -14808,6 +14895,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -14925,6 +15013,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -15042,6 +15131,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -15159,6 +15249,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -15276,6 +15367,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -15393,6 +15485,7 @@
           <t>纳入研究全文/文本/38_Ezeamuzie_2023.txt</t>
         </is>
       </c>
+      <c r="X89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -15510,6 +15603,7 @@
           <t>纳入研究全文/文本/39_Zhou_2023.txt</t>
         </is>
       </c>
+      <c r="X90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -15627,6 +15721,7 @@
           <t>纳入研究全文/文本/39_Zhou_2023.txt</t>
         </is>
       </c>
+      <c r="X91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -15744,6 +15839,7 @@
           <t>纳入研究全文/文本/42_Huang_2023.txt</t>
         </is>
       </c>
+      <c r="X92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -15861,6 +15957,7 @@
           <t>纳入研究全文/文本/42_Huang_2023.txt</t>
         </is>
       </c>
+      <c r="X93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -15978,6 +16075,7 @@
           <t>纳入研究全文/文本/42_Huang_2023.txt</t>
         </is>
       </c>
+      <c r="X94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -16095,6 +16193,7 @@
           <t>纳入研究全文/文本/42_Huang_2023.txt</t>
         </is>
       </c>
+      <c r="X95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -16212,6 +16311,7 @@
           <t>纳入研究全文/文本/42_Huang_2023.txt</t>
         </is>
       </c>
+      <c r="X96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -16329,6 +16429,7 @@
           <t>纳入研究全文/文本/44_Gerosa_2022.txt</t>
         </is>
       </c>
+      <c r="X97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -16446,6 +16547,7 @@
           <t>纳入研究全文/文本/47_Ozcan_2021.txt</t>
         </is>
       </c>
+      <c r="X98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -16563,6 +16665,7 @@
           <t>纳入研究全文/文本/47_Ozcan_2021.txt</t>
         </is>
       </c>
+      <c r="X99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -16680,6 +16783,7 @@
           <t>纳入研究全文/文本/47_Ozcan_2021.txt</t>
         </is>
       </c>
+      <c r="X100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -16797,6 +16901,7 @@
           <t>纳入研究全文/文本/52_Arık_2022.txt</t>
         </is>
       </c>
+      <c r="X101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -16914,6 +17019,7 @@
           <t>纳入研究全文/文本/52_Arık_2022.txt</t>
         </is>
       </c>
+      <c r="X102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -17031,6 +17137,7 @@
           <t>纳入研究全文/文本/53_Sáez-López_2019.txt</t>
         </is>
       </c>
+      <c r="X103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -17148,6 +17255,7 @@
           <t>纳入研究全文/文本/53_Sáez-López_2019.txt</t>
         </is>
       </c>
+      <c r="X104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -17265,6 +17373,7 @@
           <t>纳入研究全文/文本/56_Fanchamps_2021.txt</t>
         </is>
       </c>
+      <c r="X105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -17382,6 +17491,7 @@
           <t>纳入研究全文/文本/56_Fanchamps_2021.txt</t>
         </is>
       </c>
+      <c r="X106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -17499,6 +17609,7 @@
           <t>纳入研究全文/文本/56_Fanchamps_2021.txt</t>
         </is>
       </c>
+      <c r="X107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -17616,6 +17727,7 @@
           <t>纳入研究全文/文本/60_Nguyen_2021.txt</t>
         </is>
       </c>
+      <c r="X108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -17733,6 +17845,7 @@
           <t>纳入研究全文/文本/60_Nguyen_2021.txt</t>
         </is>
       </c>
+      <c r="X109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -17850,6 +17963,7 @@
           <t>纳入研究全文/文本/60_Nguyen_2021.txt</t>
         </is>
       </c>
+      <c r="X110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -17967,6 +18081,7 @@
           <t>纳入研究全文/文本/61_Nogueira_2022.txt</t>
         </is>
       </c>
+      <c r="X111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -18084,6 +18199,7 @@
           <t>纳入研究全文/文本/62_Ragonis_2018.txt</t>
         </is>
       </c>
+      <c r="X112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -18201,6 +18317,7 @@
           <t>纳入研究全文/文本/62_Ragonis_2018.txt</t>
         </is>
       </c>
+      <c r="X113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -18318,6 +18435,7 @@
           <t>纳入研究全文/文本/62_Ragonis_2018.txt</t>
         </is>
       </c>
+      <c r="X114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -18435,6 +18553,7 @@
           <t>纳入研究全文/文本/62_Ragonis_2018.txt</t>
         </is>
       </c>
+      <c r="X115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -18552,6 +18671,7 @@
           <t>纳入研究全文/文本/64_Refvik_2023.txt</t>
         </is>
       </c>
+      <c r="X116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -18669,6 +18789,7 @@
           <t>纳入研究全文/文本/66_Jenkins_2015.txt</t>
         </is>
       </c>
+      <c r="X117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -18786,6 +18907,7 @@
           <t>纳入研究全文/文本/66_Jenkins_2015.txt</t>
         </is>
       </c>
+      <c r="X118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -18903,6 +19025,7 @@
           <t>纳入研究全文/文本/67_Ortiz_2015.txt</t>
         </is>
       </c>
+      <c r="X119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -19020,6 +19143,7 @@
           <t>纳入研究全文/文本/67_Ortiz_2015.txt</t>
         </is>
       </c>
+      <c r="X120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -19137,6 +19261,7 @@
           <t>纳入研究全文/文本/67_Ortiz_2015.txt</t>
         </is>
       </c>
+      <c r="X121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -19254,6 +19379,7 @@
           <t>纳入研究全文/文本/67_Ortiz_2015.txt</t>
         </is>
       </c>
+      <c r="X122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -19371,6 +19497,7 @@
           <t>纳入研究全文/文本/68_Yi-Eu_2016.txt</t>
         </is>
       </c>
+      <c r="X123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -19488,6 +19615,7 @@
           <t>纳入研究全文/文本/69_Owston_2009.txt</t>
         </is>
       </c>
+      <c r="X124" s="5" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -19605,6 +19733,7 @@
           <t>纳入研究全文/文本/69_Owston_2009.txt</t>
         </is>
       </c>
+      <c r="X125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -19722,6 +19851,7 @@
           <t>纳入研究全文/文本/69_Owston_2009.txt</t>
         </is>
       </c>
+      <c r="X126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -19839,6 +19969,7 @@
           <t>纳入研究全文/文本/70_Saba_2023.txt</t>
         </is>
       </c>
+      <c r="X127" s="5" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -19956,6 +20087,7 @@
           <t>纳入研究全文/文本/70_Saba_2023.txt</t>
         </is>
       </c>
+      <c r="X128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -20073,6 +20205,7 @@
           <t>纳入研究全文/文本/71_Kara-Zorluoglu-Ceyhan_2026.txt</t>
         </is>
       </c>
+      <c r="X129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -20190,6 +20323,7 @@
           <t>纳入研究全文/文本/72_Pardamean_2015.txt</t>
         </is>
       </c>
+      <c r="X130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -20307,6 +20441,7 @@
           <t>纳入研究全文/文本/72_Pardamean_2015.txt</t>
         </is>
       </c>
+      <c r="X131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -20424,6 +20559,7 @@
           <t>纳入研究全文/文本/72_Pardamean_2015.txt</t>
         </is>
       </c>
+      <c r="X132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -20541,6 +20677,7 @@
           <t>纳入研究全文/文本/72_Pardamean_2015.txt</t>
         </is>
       </c>
+      <c r="X133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -20658,6 +20795,7 @@
           <t>纳入研究全文/文本/73_Calao_2015.txt</t>
         </is>
       </c>
+      <c r="X134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -20775,6 +20913,7 @@
           <t>纳入研究全文/文本/74_Tang-Ma_2022.txt</t>
         </is>
       </c>
+      <c r="X135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -20892,6 +21031,7 @@
           <t>纳入研究全文/文本/75_Hijón-Neira_2024.txt</t>
         </is>
       </c>
+      <c r="X136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -21009,6 +21149,7 @@
           <t>纳入研究全文/文本/76_Fitrah_2025.txt</t>
         </is>
       </c>
+      <c r="X137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -21126,6 +21267,7 @@
           <t>纳入研究全文/文本/76_Fitrah_2025.txt</t>
         </is>
       </c>
+      <c r="X138" s="5" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -21243,6 +21385,7 @@
           <t>纳入研究全文/文本/76_Fitrah_2025.txt</t>
         </is>
       </c>
+      <c r="X139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -21360,6 +21503,7 @@
           <t>纳入研究全文/文本/76_Fitrah_2025.txt</t>
         </is>
       </c>
+      <c r="X140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -21477,6 +21621,7 @@
           <t>纳入研究全文/文本/77_Setyawarno_2026.txt</t>
         </is>
       </c>
+      <c r="X141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -21594,6 +21739,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -21711,6 +21857,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X143" s="5" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -21828,6 +21975,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -21945,6 +22093,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X145" s="5" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -22062,6 +22211,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X146" s="5" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -22179,6 +22329,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X147" s="5" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -22296,6 +22447,7 @@
           <t>纳入研究全文/文本/78_Montuori_2023.txt</t>
         </is>
       </c>
+      <c r="X148" s="5" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -22413,6 +22565,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -22530,6 +22683,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -22647,6 +22801,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -22764,6 +22919,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X152" s="5" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -22881,6 +23037,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X153" s="5" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -22998,6 +23155,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -23115,6 +23273,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -23232,6 +23391,7 @@
           <t>纳入研究全文/文本/79_Näslund-Hadley_2026.txt</t>
         </is>
       </c>
+      <c r="X156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -23349,6 +23509,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X157" s="5" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -23466,6 +23627,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X158" s="5" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -23583,6 +23745,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -23700,6 +23863,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X160" s="5" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -23817,6 +23981,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -23934,6 +24099,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X162" s="5" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -24051,6 +24217,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X163" s="5" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -24168,6 +24335,7 @@
           <t>纳入研究全文/文本/80_Yusuf_2024.txt</t>
         </is>
       </c>
+      <c r="X164" s="5" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -24285,6 +24453,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X165" s="5" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -24402,6 +24571,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X166" s="5" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -24519,6 +24689,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -24636,6 +24807,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -24753,6 +24925,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X169" s="5" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -24870,6 +25043,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X170" s="5" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -24987,6 +25161,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X171" s="5" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -25104,6 +25279,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X172" s="5" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -25221,6 +25397,7 @@
           <t>纳入研究全文/文本/81_Chen_2024.txt</t>
         </is>
       </c>
+      <c r="X173" s="5" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -25338,6 +25515,7 @@
           <t>纳入研究全文/文本/82_Ahmed_2025.txt</t>
         </is>
       </c>
+      <c r="X174" s="5" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -25455,6 +25633,7 @@
           <t>纳入研究全文/文本/83_Amirbek_2026.txt</t>
         </is>
       </c>
+      <c r="X175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -25572,6 +25751,7 @@
           <t>纳入研究全文/文本/83_Amirbek_2026.txt</t>
         </is>
       </c>
+      <c r="X176" s="5" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -25689,8 +25869,9 @@
           <t>纳入研究全文/文本/83_Amirbek_2026.txt</t>
         </is>
       </c>
-    </row>
-    <row r="178">
+      <c r="X177" s="5" t="inlineStr"/>
+    </row>
+    <row r="178" ht="34" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
         <is>
           <t>E0296</t>
@@ -25804,6 +25985,11 @@
       <c r="W178" s="5" t="inlineStr">
         <is>
           <t>纳入研究全文/文本/84_García_2022.txt</t>
+        </is>
+      </c>
+      <c r="X178" s="6" t="inlineStr">
+        <is>
+          <t>资格存疑；计入231条总体；230条／64项研究作敏感性排除</t>
         </is>
       </c>
     </row>
@@ -25923,6 +26109,7 @@
           <t>纳入研究全文/文本/85_Xian_2026.txt</t>
         </is>
       </c>
+      <c r="X179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -26040,6 +26227,7 @@
           <t>纳入研究全文/文本/85_Xian_2026.txt</t>
         </is>
       </c>
+      <c r="X180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -26157,6 +26345,7 @@
           <t>纳入研究全文/文本/86_Robledo-Castro_2023.txt</t>
         </is>
       </c>
+      <c r="X181" s="5" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -26274,6 +26463,7 @@
           <t>纳入研究全文/文本/87_Aissa_2025.txt</t>
         </is>
       </c>
+      <c r="X182" s="5" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -26391,6 +26581,7 @@
           <t>纳入研究全文/文本/88_Cheng_2022.txt</t>
         </is>
       </c>
+      <c r="X183" s="5" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -26508,6 +26699,7 @@
           <t>纳入研究全文/文本/89_Sun_2025.txt</t>
         </is>
       </c>
+      <c r="X184" s="5" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -26625,6 +26817,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X185" s="5" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -26742,6 +26935,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X186" s="5" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -26859,6 +27053,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X187" s="5" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -26976,6 +27171,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X188" s="5" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -27093,6 +27289,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X189" s="5" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -27210,6 +27407,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X190" s="5" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -27327,6 +27525,7 @@
           <t>纳入研究全文/文本/90_Yolcu_2023.txt</t>
         </is>
       </c>
+      <c r="X191" s="5" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -27444,6 +27643,7 @@
           <t>纳入研究全文/文本/91_Alrawashdeh_2026.txt</t>
         </is>
       </c>
+      <c r="X192" s="5" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -27561,6 +27761,7 @@
           <t>纳入研究全文/文本/92_Basu_2017.txt</t>
         </is>
       </c>
+      <c r="X193" s="5" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -27678,6 +27879,7 @@
           <t>纳入研究全文/文本/93_Mercan_2026.txt</t>
         </is>
       </c>
+      <c r="X194" s="5" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -27795,6 +27997,7 @@
           <t>纳入研究全文/文本/93_Mercan_2026.txt</t>
         </is>
       </c>
+      <c r="X195" s="5" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -27912,6 +28115,7 @@
           <t>纳入研究全文/文本/93_Mercan_2026.txt</t>
         </is>
       </c>
+      <c r="X196" s="5" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -28029,6 +28233,7 @@
           <t>纳入研究全文/文本/94_Noguera_2026.txt</t>
         </is>
       </c>
+      <c r="X197" s="5" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -28146,6 +28351,7 @@
           <t>纳入研究全文/文本/94_Noguera_2026.txt</t>
         </is>
       </c>
+      <c r="X198" s="5" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -28263,6 +28469,7 @@
           <t>纳入研究全文/文本/95_Lin_2021.txt</t>
         </is>
       </c>
+      <c r="X199" s="5" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -28380,6 +28587,7 @@
           <t>纳入研究全文/文本/95_Lin_2021.txt</t>
         </is>
       </c>
+      <c r="X200" s="5" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -28497,6 +28705,7 @@
           <t>纳入研究全文/文本/96_Lin_2024.txt</t>
         </is>
       </c>
+      <c r="X201" s="5" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -28614,6 +28823,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X202" s="5" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -28731,6 +28941,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X203" s="5" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -28848,6 +29059,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X204" s="5" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -28965,6 +29177,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X205" s="5" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -29082,6 +29295,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X206" s="5" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -29199,6 +29413,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X207" s="5" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -29316,6 +29531,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X208" s="5" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -29433,6 +29649,7 @@
           <t>纳入研究全文/文本/97_Gao-Hew_2022.txt</t>
         </is>
       </c>
+      <c r="X209" s="5" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -29550,6 +29767,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X210" s="5" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -29667,6 +29885,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X211" s="5" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -29784,6 +30003,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X212" s="5" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -29901,6 +30121,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X213" s="5" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -30018,6 +30239,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X214" s="5" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -30135,6 +30357,7 @@
           <t>纳入研究全文/文本/98_Wu-Chen_2022.txt</t>
         </is>
       </c>
+      <c r="X215" s="5" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -30252,6 +30475,7 @@
           <t>纳入研究全文/文本/99_Gao-Hew_2023.txt</t>
         </is>
       </c>
+      <c r="X216" s="5" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -30369,6 +30593,7 @@
           <t>纳入研究全文/文本/99_Gao-Hew_2023.txt</t>
         </is>
       </c>
+      <c r="X217" s="5" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -30486,6 +30711,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X218" s="5" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -30603,6 +30829,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X219" s="5" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -30720,6 +30947,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X220" s="5" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -30837,6 +31065,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X221" s="5" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -30954,6 +31183,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X222" s="5" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -31071,6 +31301,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X223" s="5" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -31188,6 +31419,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X224" s="5" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -31305,6 +31537,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X225" s="5" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -31422,6 +31655,7 @@
           <t>纳入研究全文/文本/100_Lee_2024.txt</t>
         </is>
       </c>
+      <c r="X226" s="5" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -31539,6 +31773,7 @@
           <t>纳入研究全文/文本/101_Sun-Liu_2024.txt</t>
         </is>
       </c>
+      <c r="X227" s="5" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -31656,6 +31891,7 @@
           <t>纳入研究全文/文本/101_Sun-Liu_2024.txt</t>
         </is>
       </c>
+      <c r="X228" s="5" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -31773,6 +32009,7 @@
           <t>纳入研究全文/文本/101_Sun-Liu_2024.txt</t>
         </is>
       </c>
+      <c r="X229" s="5" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -31890,6 +32127,7 @@
           <t>纳入研究全文/文本/101_Sun-Liu_2024.txt</t>
         </is>
       </c>
+      <c r="X230" s="5" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -32007,6 +32245,7 @@
           <t>纳入研究全文/文本/103_Zhao_2025.txt</t>
         </is>
       </c>
+      <c r="X231" s="5" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -32124,6 +32363,7 @@
           <t>纳入研究全文/文本/104_Gao_2025.txt</t>
         </is>
       </c>
+      <c r="X232" s="5" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -32241,6 +32481,7 @@
           <t>纳入研究全文/文本/104_Gao_2025.txt</t>
         </is>
       </c>
+      <c r="X233" s="5" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -32358,6 +32599,7 @@
           <t>纳入研究全文/文本/104_Gao_2025.txt</t>
         </is>
       </c>
+      <c r="X234" s="5" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -32475,6 +32717,7 @@
           <t>纳入研究全文/文本/104_Gao_2025.txt</t>
         </is>
       </c>
+      <c r="X235" s="5" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -32592,6 +32835,7 @@
           <t>纳入研究全文/文本/104_Gao_2025.txt</t>
         </is>
       </c>
+      <c r="X236" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41924,11 +42168,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41989,7 +42233,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>含效应量标识、研究序号、结局变量与时点、资格类别、任务差异类型、迁移距离、证据档位、缺口代码、两道闸门与范围闸门、集合归属、效应量与抽样方差、题录与全文相对路径。</t>
+          <t>含效应量标识、研究序号、结局变量与时点、资格类别、任务差异类型、迁移距离、证据档位、缺口代码、两道闸门与范围闸门、集合归属、效应量与抽样方差、题录与全文相对路径及正文分析处理。</t>
         </is>
       </c>
     </row>
@@ -42005,13 +42249,49 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>García（2022）锁定编码</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>表2保留“U-不属主池”；正文分析范围决定不构成锁定编码改判。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>García（2022）效应量</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>原文配对t检验不用于组间换算；g由两独立组后测均值、方差和人数计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>García（2022）正文分析</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>任务资格存疑，计入231条总体；排除后的230条、64项研究作为范围敏感性分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>表3 113 项纳入研究文献列表</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>序号与表1、表2 一致的完整题录、DOI 与核验状态。</t>
         </is>
